--- a/output/数据收集进展.xlsx
+++ b/output/数据收集进展.xlsx
@@ -646,7 +646,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>239 条</t>
+          <t>279 条</t>
         </is>
       </c>
       <c r="B5" s="4" t="n"/>
@@ -664,7 +664,7 @@
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>33 篇</t>
+          <t>34 篇</t>
         </is>
       </c>
       <c r="H5" s="4" t="n"/>
@@ -698,19 +698,19 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>162 条</t>
+          <t>189 条</t>
         </is>
       </c>
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>54 条</t>
+          <t>62 条</t>
         </is>
       </c>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>93 条</t>
+          <t>102 条</t>
         </is>
       </c>
       <c r="F7" s="4" t="n"/>
@@ -1227,16 +1227,16 @@
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>239</v>
+        <v>279</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="H25" s="9" t="n"/>
     </row>
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G30" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>162/239 (68%)</t>
+          <t>189/279 (68%)</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>54/239 (23%)</t>
+          <t>62/279 (22%)</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>93/239 (39%)</t>
+          <t>102/279 (37%)</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>139:77:23</t>
+          <t>161:91:27</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>地被层23条(10%)，仍需重点补充</t>
+          <t>地被层27条(10%)，仍需重点补充</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>192:47</t>
+          <t>232:47</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="B19" s="17" t="n"/>
       <c r="C19" s="9" t="n">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="D19" s="9" t="n">
         <v>21</v>
@@ -2880,7 +2880,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H19" s="9" t="n">
         <v>12</v>
@@ -2904,7 +2904,7 @@
         <v>0</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>239</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20"/>
@@ -3543,22 +3543,22 @@
         <v>15</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>239</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -3576,7 +3576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3589,7 +3589,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>参考文献清单（共 33 篇）</t>
+          <t>参考文献清单（共 34 篇）</t>
         </is>
       </c>
     </row>
@@ -3815,11 +3815,11 @@
       </c>
       <c r="C13" s="8" t="inlineStr"/>
       <c r="D13" s="8" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>二球悬铃木, 女贞, 广玉兰, 杜鹃, 桂花, 海桐, 石楠, 香樟, 麦冬</t>
+          <t>二球悬铃木, 女贞, 广玉兰, 杜鹃, 枫杨, 枫香, 栾树, 桂花, 水杉, 海桐, 狗牙根, 石楠, 紫薇, 香樟, 鸡爪槭, 麦冬</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
       </c>
       <c r="C15" s="8" t="inlineStr"/>
       <c r="D15" s="8" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>八角金盘, 广玉兰, 杜鹃, 桂花, 红叶石楠, 红花檵木, 香樟</t>
+          <t>八角金盘, 吉祥草, 广玉兰, 日本晚樱, 杜英, 杜鹃, 柚子树, 栀子, 桂花, 棕榈, 珊瑚树, 紫叶李, 红叶石楠, 红花檵木, 香樟, 鸢尾</t>
         </is>
       </c>
     </row>
@@ -4197,11 +4197,11 @@
       </c>
       <c r="C31" s="8" t="inlineStr"/>
       <c r="D31" s="8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>广玉兰, 桂花, 红叶石楠, 香樟</t>
+          <t>山茶, 广玉兰, 杜英, 杨梅, 柚子树, 桂花, 法国冬青, 紫叶李, 红叶石楠, 香樟</t>
         </is>
       </c>
     </row>
@@ -4239,11 +4239,11 @@
       </c>
       <c r="C33" s="8" t="inlineStr"/>
       <c r="D33" s="8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>二球悬铃木, 八角金盘, 杜鹃, 桂花, 洒金桃叶珊瑚, 红花檵木</t>
+          <t>二球悬铃木, 光叶石楠, 八角金盘, 小叶黄杨, 望江南, 杜鹃, 栀子, 桂花, 洒金桃叶珊瑚, 火棘, 珊瑚树, 紫叶李, 紫薇, 红花檵木, 银杏, 鸡爪槭</t>
         </is>
       </c>
     </row>
@@ -4313,6 +4313,25 @@
       <c r="E36" s="8" t="inlineStr">
         <is>
           <t>二球悬铃木, 香樟</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>刘青,刘苑秋,赖发英, 2009, 江西农业大学学报, 31(6):1063-1068</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr"/>
+      <c r="D37" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>红翅槭, 罗汉松</t>
         </is>
       </c>
     </row>
@@ -4330,11 +4349,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U240"/>
+  <dimension ref="A1:U280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -22440,6 +22459,2728 @@
         </is>
       </c>
     </row>
+    <row r="241">
+      <c r="A241" s="8" t="inlineStr">
+        <is>
+          <t>银杏</t>
+        </is>
+      </c>
+      <c r="B241" s="8" t="inlineStr">
+        <is>
+          <t>Ginkgo biloba</t>
+        </is>
+      </c>
+      <c r="C241" s="8" t="inlineStr">
+        <is>
+          <t>乔木</t>
+        </is>
+      </c>
+      <c r="D241" s="8" t="inlineStr">
+        <is>
+          <t>交通干道</t>
+        </is>
+      </c>
+      <c r="E241" s="8" t="n">
+        <v>1.0033</v>
+      </c>
+      <c r="F241" s="8" t="inlineStr"/>
+      <c r="G241" s="8" t="inlineStr"/>
+      <c r="H241" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I241" s="8" t="inlineStr"/>
+      <c r="J241" s="8" t="inlineStr"/>
+      <c r="K241" s="8" t="inlineStr"/>
+      <c r="L241" s="8" t="inlineStr"/>
+      <c r="M241" s="8" t="inlineStr">
+        <is>
+          <t>夏季</t>
+        </is>
+      </c>
+      <c r="N241" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="O241" s="8" t="inlineStr"/>
+      <c r="P241" s="8" t="inlineStr">
+        <is>
+          <t>滤膜称重法</t>
+        </is>
+      </c>
+      <c r="Q241" s="8" t="inlineStr">
+        <is>
+          <t>上表皮细胞长条形具波状弯曲,垂周壁下陷成浅沟状,平周壁突起,表面光滑,无气孔及毛被;下表皮气孔器较多略下陷无毛被</t>
+        </is>
+      </c>
+      <c r="R241" s="8" t="inlineStr">
+        <is>
+          <t>余曼,汪正祥,雷耘等, 2009, 环境工程学报, 3(7):1333-1339</t>
+        </is>
+      </c>
+      <c r="S241" s="8" t="inlineStr"/>
+      <c r="T241" s="8" t="inlineStr">
+        <is>
+          <t>武汉一环线解放大道,大雨后7d采样,16树种中滞尘倒数第2</t>
+        </is>
+      </c>
+      <c r="U241" s="8" t="inlineStr">
+        <is>
+          <t>交通干道</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="8" t="inlineStr">
+        <is>
+          <t>紫薇</t>
+        </is>
+      </c>
+      <c r="B242" s="8" t="inlineStr">
+        <is>
+          <t>Lagerstroemia indica</t>
+        </is>
+      </c>
+      <c r="C242" s="8" t="inlineStr">
+        <is>
+          <t>乔木</t>
+        </is>
+      </c>
+      <c r="D242" s="8" t="inlineStr">
+        <is>
+          <t>交通干道</t>
+        </is>
+      </c>
+      <c r="E242" s="8" t="n">
+        <v>1.9543</v>
+      </c>
+      <c r="F242" s="8" t="inlineStr"/>
+      <c r="G242" s="8" t="inlineStr"/>
+      <c r="H242" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I242" s="8" t="inlineStr"/>
+      <c r="J242" s="8" t="inlineStr"/>
+      <c r="K242" s="8" t="inlineStr"/>
+      <c r="L242" s="8" t="inlineStr"/>
+      <c r="M242" s="8" t="inlineStr">
+        <is>
+          <t>夏季</t>
+        </is>
+      </c>
+      <c r="N242" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="O242" s="8" t="inlineStr"/>
+      <c r="P242" s="8" t="inlineStr">
+        <is>
+          <t>滤膜称重法</t>
+        </is>
+      </c>
+      <c r="Q242" s="8" t="inlineStr">
+        <is>
+          <t>上表皮凹凸不平有不规则褶皱,脊状突起和凹陷起伏大;下表皮气孔器深陷于褶皱凹陷中</t>
+        </is>
+      </c>
+      <c r="R242" s="8" t="inlineStr">
+        <is>
+          <t>余曼,汪正祥,雷耘等, 2009, 环境工程学报, 3(7):1333-1339</t>
+        </is>
+      </c>
+      <c r="S242" s="8" t="inlineStr"/>
+      <c r="T242" s="8" t="inlineStr">
+        <is>
+          <t>武汉一环线解放大道,小乔木中滞尘最强</t>
+        </is>
+      </c>
+      <c r="U242" s="8" t="inlineStr">
+        <is>
+          <t>交通干道</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="8" t="inlineStr">
+        <is>
+          <t>紫叶李</t>
+        </is>
+      </c>
+      <c r="B243" s="8" t="inlineStr">
+        <is>
+          <t>Prunus cerasifera f. atropurpurea</t>
+        </is>
+      </c>
+      <c r="C243" s="8" t="inlineStr">
+        <is>
+          <t>乔木</t>
+        </is>
+      </c>
+      <c r="D243" s="8" t="inlineStr">
+        <is>
+          <t>交通干道</t>
+        </is>
+      </c>
+      <c r="E243" s="8" t="n">
+        <v>1.879</v>
+      </c>
+      <c r="F243" s="8" t="inlineStr"/>
+      <c r="G243" s="8" t="inlineStr"/>
+      <c r="H243" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I243" s="8" t="inlineStr"/>
+      <c r="J243" s="8" t="inlineStr"/>
+      <c r="K243" s="8" t="inlineStr"/>
+      <c r="L243" s="8" t="inlineStr"/>
+      <c r="M243" s="8" t="inlineStr">
+        <is>
+          <t>夏季</t>
+        </is>
+      </c>
+      <c r="N243" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="O243" s="8" t="inlineStr"/>
+      <c r="P243" s="8" t="inlineStr">
+        <is>
+          <t>滤膜称重法</t>
+        </is>
+      </c>
+      <c r="Q243" s="8" t="inlineStr">
+        <is>
+          <t>原文未做SEM扫描</t>
+        </is>
+      </c>
+      <c r="R243" s="8" t="inlineStr">
+        <is>
+          <t>余曼,汪正祥,雷耘等, 2009, 环境工程学报, 3(7):1333-1339</t>
+        </is>
+      </c>
+      <c r="S243" s="8" t="inlineStr"/>
+      <c r="T243" s="8" t="inlineStr">
+        <is>
+          <t>武汉一环线解放大道,小乔木中滞尘第2</t>
+        </is>
+      </c>
+      <c r="U243" s="8" t="inlineStr">
+        <is>
+          <t>交通干道</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="8" t="inlineStr">
+        <is>
+          <t>鸡爪槭</t>
+        </is>
+      </c>
+      <c r="B244" s="8" t="inlineStr">
+        <is>
+          <t>Acer palmatum</t>
+        </is>
+      </c>
+      <c r="C244" s="8" t="inlineStr">
+        <is>
+          <t>乔木</t>
+        </is>
+      </c>
+      <c r="D244" s="8" t="inlineStr">
+        <is>
+          <t>交通干道</t>
+        </is>
+      </c>
+      <c r="E244" s="8" t="n">
+        <v>0.7852</v>
+      </c>
+      <c r="F244" s="8" t="inlineStr"/>
+      <c r="G244" s="8" t="inlineStr"/>
+      <c r="H244" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I244" s="8" t="inlineStr"/>
+      <c r="J244" s="8" t="inlineStr"/>
+      <c r="K244" s="8" t="inlineStr"/>
+      <c r="L244" s="8" t="inlineStr"/>
+      <c r="M244" s="8" t="inlineStr">
+        <is>
+          <t>夏季</t>
+        </is>
+      </c>
+      <c r="N244" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="O244" s="8" t="inlineStr"/>
+      <c r="P244" s="8" t="inlineStr">
+        <is>
+          <t>滤膜称重法</t>
+        </is>
+      </c>
+      <c r="Q244" s="8" t="inlineStr">
+        <is>
+          <t>上表皮六边形细胞,平周壁凹陷垂周壁凸起形成网格;下表皮气孔密集凸出,副卫细胞平轴式排列;叶片革质5-7裂易振动脱尘</t>
+        </is>
+      </c>
+      <c r="R244" s="8" t="inlineStr">
+        <is>
+          <t>余曼,汪正祥,雷耘等, 2009, 环境工程学报, 3(7):1333-1339</t>
+        </is>
+      </c>
+      <c r="S244" s="8" t="inlineStr"/>
+      <c r="T244" s="8" t="inlineStr">
+        <is>
+          <t>武汉一环线解放大道,16树种中滞尘最低</t>
+        </is>
+      </c>
+      <c r="U244" s="8" t="inlineStr">
+        <is>
+          <t>交通干道</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="8" t="inlineStr">
+        <is>
+          <t>珊瑚树</t>
+        </is>
+      </c>
+      <c r="B245" s="8" t="inlineStr">
+        <is>
+          <t>Viburnum odoratissimum</t>
+        </is>
+      </c>
+      <c r="C245" s="8" t="inlineStr">
+        <is>
+          <t>灌木</t>
+        </is>
+      </c>
+      <c r="D245" s="8" t="inlineStr">
+        <is>
+          <t>交通干道</t>
+        </is>
+      </c>
+      <c r="E245" s="8" t="n">
+        <v>3.1527</v>
+      </c>
+      <c r="F245" s="8" t="inlineStr"/>
+      <c r="G245" s="8" t="inlineStr"/>
+      <c r="H245" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I245" s="8" t="inlineStr"/>
+      <c r="J245" s="8" t="inlineStr"/>
+      <c r="K245" s="8" t="inlineStr"/>
+      <c r="L245" s="8" t="inlineStr"/>
+      <c r="M245" s="8" t="inlineStr">
+        <is>
+          <t>夏季</t>
+        </is>
+      </c>
+      <c r="N245" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="O245" s="8" t="inlineStr"/>
+      <c r="P245" s="8" t="inlineStr">
+        <is>
+          <t>滤膜称重法</t>
+        </is>
+      </c>
+      <c r="Q245" s="8" t="inlineStr">
+        <is>
+          <t>上表皮30μm孔穴型凹陷不规则分布;下表皮气孔器周围角质层加厚,细胞放射状平行排列</t>
+        </is>
+      </c>
+      <c r="R245" s="8" t="inlineStr">
+        <is>
+          <t>余曼,汪正祥,雷耘等, 2009, 环境工程学报, 3(7):1333-1339</t>
+        </is>
+      </c>
+      <c r="S245" s="8" t="inlineStr"/>
+      <c r="T245" s="8" t="inlineStr">
+        <is>
+          <t>武汉一环线解放大道,亦称法国冬青/日本珊瑚树</t>
+        </is>
+      </c>
+      <c r="U245" s="8" t="inlineStr">
+        <is>
+          <t>交通干道</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="8" t="inlineStr">
+        <is>
+          <t>光叶石楠</t>
+        </is>
+      </c>
+      <c r="B246" s="8" t="inlineStr">
+        <is>
+          <t>Photinia glabra</t>
+        </is>
+      </c>
+      <c r="C246" s="8" t="inlineStr">
+        <is>
+          <t>灌木</t>
+        </is>
+      </c>
+      <c r="D246" s="8" t="inlineStr">
+        <is>
+          <t>交通干道</t>
+        </is>
+      </c>
+      <c r="E246" s="8" t="n">
+        <v>2.9428</v>
+      </c>
+      <c r="F246" s="8" t="inlineStr"/>
+      <c r="G246" s="8" t="inlineStr"/>
+      <c r="H246" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I246" s="8" t="inlineStr"/>
+      <c r="J246" s="8" t="inlineStr"/>
+      <c r="K246" s="8" t="inlineStr"/>
+      <c r="L246" s="8" t="inlineStr"/>
+      <c r="M246" s="8" t="inlineStr">
+        <is>
+          <t>夏季</t>
+        </is>
+      </c>
+      <c r="N246" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="O246" s="8" t="inlineStr"/>
+      <c r="P246" s="8" t="inlineStr">
+        <is>
+          <t>滤膜称重法</t>
+        </is>
+      </c>
+      <c r="Q246" s="8" t="inlineStr">
+        <is>
+          <t>原文未做SEM扫描</t>
+        </is>
+      </c>
+      <c r="R246" s="8" t="inlineStr">
+        <is>
+          <t>余曼,汪正祥,雷耘等, 2009, 环境工程学报, 3(7):1333-1339</t>
+        </is>
+      </c>
+      <c r="S246" s="8" t="inlineStr"/>
+      <c r="T246" s="8" t="inlineStr">
+        <is>
+          <t>武汉一环线解放大道;注:光叶石楠≠红叶石楠(Photinia×fraseri)</t>
+        </is>
+      </c>
+      <c r="U246" s="8" t="inlineStr">
+        <is>
+          <t>交通干道</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="8" t="inlineStr">
+        <is>
+          <t>火棘</t>
+        </is>
+      </c>
+      <c r="B247" s="8" t="inlineStr">
+        <is>
+          <t>Pyracantha fortuneana</t>
+        </is>
+      </c>
+      <c r="C247" s="8" t="inlineStr">
+        <is>
+          <t>灌木</t>
+        </is>
+      </c>
+      <c r="D247" s="8" t="inlineStr">
+        <is>
+          <t>交通干道</t>
+        </is>
+      </c>
+      <c r="E247" s="8" t="n">
+        <v>2.3044</v>
+      </c>
+      <c r="F247" s="8" t="inlineStr"/>
+      <c r="G247" s="8" t="inlineStr"/>
+      <c r="H247" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I247" s="8" t="inlineStr"/>
+      <c r="J247" s="8" t="inlineStr"/>
+      <c r="K247" s="8" t="inlineStr"/>
+      <c r="L247" s="8" t="inlineStr"/>
+      <c r="M247" s="8" t="inlineStr">
+        <is>
+          <t>夏季</t>
+        </is>
+      </c>
+      <c r="N247" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="O247" s="8" t="inlineStr"/>
+      <c r="P247" s="8" t="inlineStr">
+        <is>
+          <t>滤膜称重法</t>
+        </is>
+      </c>
+      <c r="Q247" s="8" t="inlineStr">
+        <is>
+          <t>上表皮椭圆形细胞上凸形成瘤状突起,气孔极少周围角质增厚;下表皮垂周壁下陷平周壁突起,气孔周围副卫细胞隆起呈圆环状</t>
+        </is>
+      </c>
+      <c r="R247" s="8" t="inlineStr">
+        <is>
+          <t>余曼,汪正祥,雷耘等, 2009, 环境工程学报, 3(7):1333-1339</t>
+        </is>
+      </c>
+      <c r="S247" s="8" t="inlineStr"/>
+      <c r="T247" s="8" t="inlineStr">
+        <is>
+          <t>武汉一环线解放大道</t>
+        </is>
+      </c>
+      <c r="U247" s="8" t="inlineStr">
+        <is>
+          <t>交通干道</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="8" t="inlineStr">
+        <is>
+          <t>栀子</t>
+        </is>
+      </c>
+      <c r="B248" s="8" t="inlineStr">
+        <is>
+          <t>Gardenia jasminoides</t>
+        </is>
+      </c>
+      <c r="C248" s="8" t="inlineStr">
+        <is>
+          <t>灌木</t>
+        </is>
+      </c>
+      <c r="D248" s="8" t="inlineStr">
+        <is>
+          <t>交通干道</t>
+        </is>
+      </c>
+      <c r="E248" s="8" t="n">
+        <v>1.8581</v>
+      </c>
+      <c r="F248" s="8" t="inlineStr"/>
+      <c r="G248" s="8" t="inlineStr"/>
+      <c r="H248" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I248" s="8" t="inlineStr"/>
+      <c r="J248" s="8" t="inlineStr"/>
+      <c r="K248" s="8" t="inlineStr"/>
+      <c r="L248" s="8" t="inlineStr"/>
+      <c r="M248" s="8" t="inlineStr">
+        <is>
+          <t>夏季</t>
+        </is>
+      </c>
+      <c r="N248" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="O248" s="8" t="inlineStr"/>
+      <c r="P248" s="8" t="inlineStr">
+        <is>
+          <t>滤膜称重法</t>
+        </is>
+      </c>
+      <c r="Q248" s="8" t="inlineStr">
+        <is>
+          <t>原文未做SEM扫描</t>
+        </is>
+      </c>
+      <c r="R248" s="8" t="inlineStr">
+        <is>
+          <t>余曼,汪正祥,雷耘等, 2009, 环境工程学报, 3(7):1333-1339</t>
+        </is>
+      </c>
+      <c r="S248" s="8" t="inlineStr"/>
+      <c r="T248" s="8" t="inlineStr">
+        <is>
+          <t>武汉一环线解放大道</t>
+        </is>
+      </c>
+      <c r="U248" s="8" t="inlineStr">
+        <is>
+          <t>交通干道</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="8" t="inlineStr">
+        <is>
+          <t>望江南</t>
+        </is>
+      </c>
+      <c r="B249" s="8" t="inlineStr">
+        <is>
+          <t>Cassia occidentalis</t>
+        </is>
+      </c>
+      <c r="C249" s="8" t="inlineStr">
+        <is>
+          <t>灌木</t>
+        </is>
+      </c>
+      <c r="D249" s="8" t="inlineStr">
+        <is>
+          <t>交通干道</t>
+        </is>
+      </c>
+      <c r="E249" s="8" t="n">
+        <v>1.7949</v>
+      </c>
+      <c r="F249" s="8" t="inlineStr"/>
+      <c r="G249" s="8" t="inlineStr"/>
+      <c r="H249" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I249" s="8" t="inlineStr"/>
+      <c r="J249" s="8" t="inlineStr"/>
+      <c r="K249" s="8" t="inlineStr"/>
+      <c r="L249" s="8" t="inlineStr"/>
+      <c r="M249" s="8" t="inlineStr">
+        <is>
+          <t>夏季</t>
+        </is>
+      </c>
+      <c r="N249" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="O249" s="8" t="inlineStr"/>
+      <c r="P249" s="8" t="inlineStr">
+        <is>
+          <t>滤膜称重法</t>
+        </is>
+      </c>
+      <c r="Q249" s="8" t="inlineStr">
+        <is>
+          <t>原文未做SEM扫描</t>
+        </is>
+      </c>
+      <c r="R249" s="8" t="inlineStr">
+        <is>
+          <t>余曼,汪正祥,雷耘等, 2009, 环境工程学报, 3(7):1333-1339</t>
+        </is>
+      </c>
+      <c r="S249" s="8" t="inlineStr"/>
+      <c r="T249" s="8" t="inlineStr">
+        <is>
+          <t>武汉一环线解放大道</t>
+        </is>
+      </c>
+      <c r="U249" s="8" t="inlineStr">
+        <is>
+          <t>交通干道</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="8" t="inlineStr">
+        <is>
+          <t>小叶黄杨</t>
+        </is>
+      </c>
+      <c r="B250" s="8" t="inlineStr">
+        <is>
+          <t>Buxus sinica var. parvifolia</t>
+        </is>
+      </c>
+      <c r="C250" s="8" t="inlineStr">
+        <is>
+          <t>灌木</t>
+        </is>
+      </c>
+      <c r="D250" s="8" t="inlineStr">
+        <is>
+          <t>交通干道</t>
+        </is>
+      </c>
+      <c r="E250" s="8" t="n">
+        <v>1.5041</v>
+      </c>
+      <c r="F250" s="8" t="inlineStr"/>
+      <c r="G250" s="8" t="inlineStr"/>
+      <c r="H250" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I250" s="8" t="inlineStr"/>
+      <c r="J250" s="8" t="inlineStr"/>
+      <c r="K250" s="8" t="inlineStr"/>
+      <c r="L250" s="8" t="inlineStr"/>
+      <c r="M250" s="8" t="inlineStr">
+        <is>
+          <t>夏季</t>
+        </is>
+      </c>
+      <c r="N250" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="O250" s="8" t="inlineStr"/>
+      <c r="P250" s="8" t="inlineStr">
+        <is>
+          <t>滤膜称重法</t>
+        </is>
+      </c>
+      <c r="Q250" s="8" t="inlineStr">
+        <is>
+          <t>上表皮平滑覆蜡质及蜡质颗粒物(直径约5μm);下表皮覆蜡质,气孔分布均匀,保卫细胞突出边缘平滑</t>
+        </is>
+      </c>
+      <c r="R250" s="8" t="inlineStr">
+        <is>
+          <t>余曼,汪正祥,雷耘等, 2009, 环境工程学报, 3(7):1333-1339</t>
+        </is>
+      </c>
+      <c r="S250" s="8" t="inlineStr"/>
+      <c r="T250" s="8" t="inlineStr">
+        <is>
+          <t>武汉一环线解放大道;注:小叶黄杨≠小叶女贞</t>
+        </is>
+      </c>
+      <c r="U250" s="8" t="inlineStr">
+        <is>
+          <t>交通干道</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="8" t="inlineStr">
+        <is>
+          <t>棕榈</t>
+        </is>
+      </c>
+      <c r="B251" s="8" t="inlineStr">
+        <is>
+          <t>Trachycarpus fortunei</t>
+        </is>
+      </c>
+      <c r="C251" s="8" t="inlineStr">
+        <is>
+          <t>乔木</t>
+        </is>
+      </c>
+      <c r="D251" s="8" t="inlineStr">
+        <is>
+          <t>文教区</t>
+        </is>
+      </c>
+      <c r="E251" s="8" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="F251" s="8" t="inlineStr"/>
+      <c r="G251" s="8" t="inlineStr"/>
+      <c r="H251" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I251" s="8" t="inlineStr"/>
+      <c r="J251" s="8" t="inlineStr"/>
+      <c r="K251" s="8" t="inlineStr"/>
+      <c r="L251" s="8" t="inlineStr"/>
+      <c r="M251" s="8" t="inlineStr">
+        <is>
+          <t>全年</t>
+        </is>
+      </c>
+      <c r="N251" s="8" t="inlineStr"/>
+      <c r="O251" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P251" s="8" t="inlineStr">
+        <is>
+          <t>滤膜称重法</t>
+        </is>
+      </c>
+      <c r="Q251" s="8" t="inlineStr"/>
+      <c r="R251" s="8" t="inlineStr">
+        <is>
+          <t>高丹丹, 2017, 湖北大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S251" s="8" t="inlineStr"/>
+      <c r="T251" s="8" t="inlineStr">
+        <is>
+          <t>湖北大学校园年均值;四季:春0.481/夏0.221/秋0.316/冬0.589</t>
+        </is>
+      </c>
+      <c r="U251" s="8" t="inlineStr">
+        <is>
+          <t>文教区</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="8" t="inlineStr">
+        <is>
+          <t>柚子树</t>
+        </is>
+      </c>
+      <c r="B252" s="8" t="inlineStr">
+        <is>
+          <t>Citrus maxima</t>
+        </is>
+      </c>
+      <c r="C252" s="8" t="inlineStr">
+        <is>
+          <t>乔木</t>
+        </is>
+      </c>
+      <c r="D252" s="8" t="inlineStr">
+        <is>
+          <t>文教区</t>
+        </is>
+      </c>
+      <c r="E252" s="8" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="F252" s="8" t="inlineStr"/>
+      <c r="G252" s="8" t="inlineStr"/>
+      <c r="H252" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I252" s="8" t="inlineStr"/>
+      <c r="J252" s="8" t="inlineStr"/>
+      <c r="K252" s="8" t="inlineStr"/>
+      <c r="L252" s="8" t="inlineStr"/>
+      <c r="M252" s="8" t="inlineStr">
+        <is>
+          <t>全年</t>
+        </is>
+      </c>
+      <c r="N252" s="8" t="inlineStr"/>
+      <c r="O252" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P252" s="8" t="inlineStr">
+        <is>
+          <t>滤膜称重法</t>
+        </is>
+      </c>
+      <c r="Q252" s="8" t="inlineStr">
+        <is>
+          <t>叶表面有较深沟壑,叶片较厚</t>
+        </is>
+      </c>
+      <c r="R252" s="8" t="inlineStr">
+        <is>
+          <t>高丹丹, 2017, 湖北大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S252" s="8" t="inlineStr"/>
+      <c r="T252" s="8" t="inlineStr">
+        <is>
+          <t>湖北大学校园年均值;四季:春0.577/夏0.249/秋0.335/冬0.632</t>
+        </is>
+      </c>
+      <c r="U252" s="8" t="inlineStr">
+        <is>
+          <t>文教区</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="8" t="inlineStr">
+        <is>
+          <t>杜英</t>
+        </is>
+      </c>
+      <c r="B253" s="8" t="inlineStr">
+        <is>
+          <t>Elaeocarpus decipiens</t>
+        </is>
+      </c>
+      <c r="C253" s="8" t="inlineStr">
+        <is>
+          <t>乔木</t>
+        </is>
+      </c>
+      <c r="D253" s="8" t="inlineStr">
+        <is>
+          <t>文教区</t>
+        </is>
+      </c>
+      <c r="E253" s="8" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="F253" s="8" t="inlineStr"/>
+      <c r="G253" s="8" t="inlineStr"/>
+      <c r="H253" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I253" s="8" t="inlineStr"/>
+      <c r="J253" s="8" t="inlineStr"/>
+      <c r="K253" s="8" t="inlineStr"/>
+      <c r="L253" s="8" t="inlineStr"/>
+      <c r="M253" s="8" t="inlineStr">
+        <is>
+          <t>全年</t>
+        </is>
+      </c>
+      <c r="N253" s="8" t="inlineStr"/>
+      <c r="O253" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P253" s="8" t="inlineStr">
+        <is>
+          <t>滤膜称重法</t>
+        </is>
+      </c>
+      <c r="Q253" s="8" t="inlineStr"/>
+      <c r="R253" s="8" t="inlineStr">
+        <is>
+          <t>高丹丹, 2017, 湖北大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S253" s="8" t="inlineStr"/>
+      <c r="T253" s="8" t="inlineStr">
+        <is>
+          <t>湖北大学校园年均值;四季:春0.412/夏0.136/秋0.328/冬0.593</t>
+        </is>
+      </c>
+      <c r="U253" s="8" t="inlineStr">
+        <is>
+          <t>文教区</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="8" t="inlineStr">
+        <is>
+          <t>紫叶李</t>
+        </is>
+      </c>
+      <c r="B254" s="8" t="inlineStr">
+        <is>
+          <t>Prunus cerasifera</t>
+        </is>
+      </c>
+      <c r="C254" s="8" t="inlineStr">
+        <is>
+          <t>乔木</t>
+        </is>
+      </c>
+      <c r="D254" s="8" t="inlineStr">
+        <is>
+          <t>文教区</t>
+        </is>
+      </c>
+      <c r="E254" s="8" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="F254" s="8" t="inlineStr"/>
+      <c r="G254" s="8" t="inlineStr"/>
+      <c r="H254" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I254" s="8" t="inlineStr"/>
+      <c r="J254" s="8" t="inlineStr"/>
+      <c r="K254" s="8" t="inlineStr"/>
+      <c r="L254" s="8" t="inlineStr"/>
+      <c r="M254" s="8" t="inlineStr">
+        <is>
+          <t>全年</t>
+        </is>
+      </c>
+      <c r="N254" s="8" t="inlineStr"/>
+      <c r="O254" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P254" s="8" t="inlineStr">
+        <is>
+          <t>滤膜称重法</t>
+        </is>
+      </c>
+      <c r="Q254" s="8" t="inlineStr">
+        <is>
+          <t>叶片较柔软,叶表沟壑浅</t>
+        </is>
+      </c>
+      <c r="R254" s="8" t="inlineStr">
+        <is>
+          <t>高丹丹, 2017, 湖北大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S254" s="8" t="inlineStr"/>
+      <c r="T254" s="8" t="inlineStr">
+        <is>
+          <t>湖北大学校园春/夏/秋三季均;冬季落叶;16种中排名第15</t>
+        </is>
+      </c>
+      <c r="U254" s="8" t="inlineStr">
+        <is>
+          <t>文教区</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="8" t="inlineStr">
+        <is>
+          <t>日本晚樱</t>
+        </is>
+      </c>
+      <c r="B255" s="8" t="inlineStr">
+        <is>
+          <t>Cerasus serrulata var. lannesiana</t>
+        </is>
+      </c>
+      <c r="C255" s="8" t="inlineStr">
+        <is>
+          <t>乔木</t>
+        </is>
+      </c>
+      <c r="D255" s="8" t="inlineStr">
+        <is>
+          <t>文教区</t>
+        </is>
+      </c>
+      <c r="E255" s="8" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="F255" s="8" t="inlineStr"/>
+      <c r="G255" s="8" t="inlineStr"/>
+      <c r="H255" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I255" s="8" t="inlineStr"/>
+      <c r="J255" s="8" t="inlineStr"/>
+      <c r="K255" s="8" t="inlineStr"/>
+      <c r="L255" s="8" t="inlineStr"/>
+      <c r="M255" s="8" t="inlineStr">
+        <is>
+          <t>全年</t>
+        </is>
+      </c>
+      <c r="N255" s="8" t="inlineStr"/>
+      <c r="O255" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P255" s="8" t="inlineStr">
+        <is>
+          <t>滤膜称重法</t>
+        </is>
+      </c>
+      <c r="Q255" s="8" t="inlineStr">
+        <is>
+          <t>叶片较柔软,叶表沟壑浅</t>
+        </is>
+      </c>
+      <c r="R255" s="8" t="inlineStr">
+        <is>
+          <t>高丹丹, 2017, 湖北大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S255" s="8" t="inlineStr"/>
+      <c r="T255" s="8" t="inlineStr">
+        <is>
+          <t>湖北大学校园春/夏/秋三季均;冬季落叶;16种中排名末位</t>
+        </is>
+      </c>
+      <c r="U255" s="8" t="inlineStr">
+        <is>
+          <t>文教区</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="8" t="inlineStr">
+        <is>
+          <t>栀子</t>
+        </is>
+      </c>
+      <c r="B256" s="8" t="inlineStr">
+        <is>
+          <t>Gardenia jasminoides</t>
+        </is>
+      </c>
+      <c r="C256" s="8" t="inlineStr">
+        <is>
+          <t>灌木</t>
+        </is>
+      </c>
+      <c r="D256" s="8" t="inlineStr">
+        <is>
+          <t>文教区</t>
+        </is>
+      </c>
+      <c r="E256" s="8" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="F256" s="8" t="inlineStr"/>
+      <c r="G256" s="8" t="inlineStr"/>
+      <c r="H256" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I256" s="8" t="inlineStr"/>
+      <c r="J256" s="8" t="inlineStr"/>
+      <c r="K256" s="8" t="inlineStr"/>
+      <c r="L256" s="8" t="inlineStr"/>
+      <c r="M256" s="8" t="inlineStr">
+        <is>
+          <t>全年</t>
+        </is>
+      </c>
+      <c r="N256" s="8" t="inlineStr"/>
+      <c r="O256" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P256" s="8" t="inlineStr">
+        <is>
+          <t>滤膜称重法</t>
+        </is>
+      </c>
+      <c r="Q256" s="8" t="inlineStr">
+        <is>
+          <t>叶表沟壑深,叶片宽大</t>
+        </is>
+      </c>
+      <c r="R256" s="8" t="inlineStr">
+        <is>
+          <t>高丹丹, 2017, 湖北大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S256" s="8" t="inlineStr"/>
+      <c r="T256" s="8" t="inlineStr">
+        <is>
+          <t>湖北大学校园年均值;16种中排名第4;四季:春0.808/夏0.453/秋0.640/冬0.949</t>
+        </is>
+      </c>
+      <c r="U256" s="8" t="inlineStr">
+        <is>
+          <t>文教区</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="8" t="inlineStr">
+        <is>
+          <t>珊瑚树</t>
+        </is>
+      </c>
+      <c r="B257" s="8" t="inlineStr">
+        <is>
+          <t>Viburnum odoratissimum</t>
+        </is>
+      </c>
+      <c r="C257" s="8" t="inlineStr">
+        <is>
+          <t>灌木</t>
+        </is>
+      </c>
+      <c r="D257" s="8" t="inlineStr">
+        <is>
+          <t>文教区</t>
+        </is>
+      </c>
+      <c r="E257" s="8" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="F257" s="8" t="inlineStr"/>
+      <c r="G257" s="8" t="inlineStr"/>
+      <c r="H257" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I257" s="8" t="inlineStr"/>
+      <c r="J257" s="8" t="inlineStr"/>
+      <c r="K257" s="8" t="inlineStr"/>
+      <c r="L257" s="8" t="inlineStr"/>
+      <c r="M257" s="8" t="inlineStr">
+        <is>
+          <t>全年</t>
+        </is>
+      </c>
+      <c r="N257" s="8" t="inlineStr"/>
+      <c r="O257" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P257" s="8" t="inlineStr">
+        <is>
+          <t>滤膜称重法</t>
+        </is>
+      </c>
+      <c r="Q257" s="8" t="inlineStr">
+        <is>
+          <t>叶表沟壑深,叶片宽大</t>
+        </is>
+      </c>
+      <c r="R257" s="8" t="inlineStr">
+        <is>
+          <t>高丹丹, 2017, 湖北大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S257" s="8" t="inlineStr"/>
+      <c r="T257" s="8" t="inlineStr">
+        <is>
+          <t>湖北大学校园年均值;16种中排名第1;四季:春0.988/夏0.562/秋0.721/冬1.139</t>
+        </is>
+      </c>
+      <c r="U257" s="8" t="inlineStr">
+        <is>
+          <t>文教区</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="8" t="inlineStr">
+        <is>
+          <t>吉祥草</t>
+        </is>
+      </c>
+      <c r="B258" s="8" t="inlineStr">
+        <is>
+          <t>Reineckia carnea</t>
+        </is>
+      </c>
+      <c r="C258" s="8" t="inlineStr">
+        <is>
+          <t>地被</t>
+        </is>
+      </c>
+      <c r="D258" s="8" t="inlineStr">
+        <is>
+          <t>文教区</t>
+        </is>
+      </c>
+      <c r="E258" s="8" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="F258" s="8" t="inlineStr"/>
+      <c r="G258" s="8" t="inlineStr"/>
+      <c r="H258" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I258" s="8" t="inlineStr"/>
+      <c r="J258" s="8" t="inlineStr"/>
+      <c r="K258" s="8" t="inlineStr"/>
+      <c r="L258" s="8" t="inlineStr"/>
+      <c r="M258" s="8" t="inlineStr">
+        <is>
+          <t>全年</t>
+        </is>
+      </c>
+      <c r="N258" s="8" t="inlineStr"/>
+      <c r="O258" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P258" s="8" t="inlineStr">
+        <is>
+          <t>滤膜称重法</t>
+        </is>
+      </c>
+      <c r="Q258" s="8" t="inlineStr"/>
+      <c r="R258" s="8" t="inlineStr">
+        <is>
+          <t>高丹丹, 2017, 湖北大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S258" s="8" t="inlineStr"/>
+      <c r="T258" s="8" t="inlineStr">
+        <is>
+          <t>湖北大学校园四季均值;春0.849/夏0.235/秋0.379/冬0.827</t>
+        </is>
+      </c>
+      <c r="U258" s="8" t="inlineStr">
+        <is>
+          <t>文教区</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="8" t="inlineStr">
+        <is>
+          <t>鸢尾</t>
+        </is>
+      </c>
+      <c r="B259" s="8" t="inlineStr">
+        <is>
+          <t>Iris tectorum</t>
+        </is>
+      </c>
+      <c r="C259" s="8" t="inlineStr">
+        <is>
+          <t>地被</t>
+        </is>
+      </c>
+      <c r="D259" s="8" t="inlineStr">
+        <is>
+          <t>文教区</t>
+        </is>
+      </c>
+      <c r="E259" s="8" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="F259" s="8" t="inlineStr"/>
+      <c r="G259" s="8" t="inlineStr"/>
+      <c r="H259" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I259" s="8" t="inlineStr"/>
+      <c r="J259" s="8" t="inlineStr"/>
+      <c r="K259" s="8" t="inlineStr"/>
+      <c r="L259" s="8" t="inlineStr"/>
+      <c r="M259" s="8" t="inlineStr">
+        <is>
+          <t>全年</t>
+        </is>
+      </c>
+      <c r="N259" s="8" t="inlineStr"/>
+      <c r="O259" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P259" s="8" t="inlineStr">
+        <is>
+          <t>滤膜称重法</t>
+        </is>
+      </c>
+      <c r="Q259" s="8" t="inlineStr"/>
+      <c r="R259" s="8" t="inlineStr">
+        <is>
+          <t>高丹丹, 2017, 湖北大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S259" s="8" t="inlineStr"/>
+      <c r="T259" s="8" t="inlineStr">
+        <is>
+          <t>湖北大学校园四季均值;春0.541/夏0.234/秋0.325/冬0.688</t>
+        </is>
+      </c>
+      <c r="U259" s="8" t="inlineStr">
+        <is>
+          <t>文教区</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="8" t="inlineStr">
+        <is>
+          <t>罗汉松</t>
+        </is>
+      </c>
+      <c r="B260" s="8" t="inlineStr">
+        <is>
+          <t>Podocarpus macrophyllus</t>
+        </is>
+      </c>
+      <c r="C260" s="8" t="inlineStr">
+        <is>
+          <t>乔木</t>
+        </is>
+      </c>
+      <c r="D260" s="8" t="inlineStr">
+        <is>
+          <t>交通干道</t>
+        </is>
+      </c>
+      <c r="E260" s="8" t="n">
+        <v>2.5249</v>
+      </c>
+      <c r="F260" s="8" t="inlineStr"/>
+      <c r="G260" s="8" t="inlineStr"/>
+      <c r="H260" s="8" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="I260" s="8" t="inlineStr"/>
+      <c r="J260" s="8" t="inlineStr"/>
+      <c r="K260" s="8" t="inlineStr"/>
+      <c r="L260" s="8" t="inlineStr"/>
+      <c r="M260" s="8" t="inlineStr"/>
+      <c r="N260" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="O260" s="8" t="inlineStr"/>
+      <c r="P260" s="8" t="inlineStr">
+        <is>
+          <t>滤膜称重法</t>
+        </is>
+      </c>
+      <c r="Q260" s="8" t="inlineStr"/>
+      <c r="R260" s="8" t="inlineStr">
+        <is>
+          <t>刘青,刘苑秋,赖发英, 2009, 江西农业大学学报, 31(6):1063-1068</t>
+        </is>
+      </c>
+      <c r="S260" s="8" t="inlineStr"/>
+      <c r="T260" s="8" t="inlineStr">
+        <is>
+          <t>南昌道路绿地模拟实验,15种中滞尘最强</t>
+        </is>
+      </c>
+      <c r="U260" s="8" t="inlineStr">
+        <is>
+          <t>交通干道</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="8" t="inlineStr">
+        <is>
+          <t>红翅槭</t>
+        </is>
+      </c>
+      <c r="B261" s="8" t="inlineStr">
+        <is>
+          <t>Acer fabri</t>
+        </is>
+      </c>
+      <c r="C261" s="8" t="inlineStr">
+        <is>
+          <t>乔木</t>
+        </is>
+      </c>
+      <c r="D261" s="8" t="inlineStr">
+        <is>
+          <t>交通干道</t>
+        </is>
+      </c>
+      <c r="E261" s="8" t="n">
+        <v>2.1787</v>
+      </c>
+      <c r="F261" s="8" t="inlineStr"/>
+      <c r="G261" s="8" t="inlineStr"/>
+      <c r="H261" s="8" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="I261" s="8" t="inlineStr"/>
+      <c r="J261" s="8" t="inlineStr"/>
+      <c r="K261" s="8" t="inlineStr"/>
+      <c r="L261" s="8" t="inlineStr"/>
+      <c r="M261" s="8" t="inlineStr"/>
+      <c r="N261" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="O261" s="8" t="inlineStr"/>
+      <c r="P261" s="8" t="inlineStr">
+        <is>
+          <t>滤膜称重法</t>
+        </is>
+      </c>
+      <c r="Q261" s="8" t="inlineStr"/>
+      <c r="R261" s="8" t="inlineStr">
+        <is>
+          <t>刘青,刘苑秋,赖发英, 2009, 江西农业大学学报, 31(6):1063-1068</t>
+        </is>
+      </c>
+      <c r="S261" s="8" t="inlineStr"/>
+      <c r="T261" s="8" t="inlineStr">
+        <is>
+          <t>南昌道路绿地模拟实验,15种中第2</t>
+        </is>
+      </c>
+      <c r="U261" s="8" t="inlineStr">
+        <is>
+          <t>交通干道</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="8" t="inlineStr">
+        <is>
+          <t>紫叶李</t>
+        </is>
+      </c>
+      <c r="B262" s="8" t="inlineStr">
+        <is>
+          <t>Prunus cerasifera</t>
+        </is>
+      </c>
+      <c r="C262" s="8" t="inlineStr">
+        <is>
+          <t>灌木</t>
+        </is>
+      </c>
+      <c r="D262" s="8" t="inlineStr">
+        <is>
+          <t>居住区</t>
+        </is>
+      </c>
+      <c r="E262" s="8" t="n">
+        <v>2.5123</v>
+      </c>
+      <c r="F262" s="8" t="inlineStr"/>
+      <c r="G262" s="8" t="inlineStr"/>
+      <c r="H262" s="8" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="I262" s="8" t="n">
+        <v>221.63</v>
+      </c>
+      <c r="J262" s="8" t="n">
+        <v>125.53</v>
+      </c>
+      <c r="K262" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="L262" s="8" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="M262" s="8" t="inlineStr">
+        <is>
+          <t>冬季</t>
+        </is>
+      </c>
+      <c r="N262" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="O262" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P262" s="8" t="inlineStr">
+        <is>
+          <t>水洗法+滤膜称重</t>
+        </is>
+      </c>
+      <c r="Q262" s="8" t="inlineStr"/>
+      <c r="R262" s="8" t="inlineStr">
+        <is>
+          <t>韩世明, 2017, 东华理工大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S262" s="8" t="inlineStr"/>
+      <c r="T262" s="8" t="inlineStr">
+        <is>
+          <t>红岭花园三期;第1/2/3周=2.1130/2.5325/2.8914g/m²;6种中排名第1</t>
+        </is>
+      </c>
+      <c r="U262" s="8" t="inlineStr">
+        <is>
+          <t>居住区</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="8" t="inlineStr">
+        <is>
+          <t>杜英</t>
+        </is>
+      </c>
+      <c r="B263" s="8" t="inlineStr">
+        <is>
+          <t>Elaeocarpus decipiens</t>
+        </is>
+      </c>
+      <c r="C263" s="8" t="inlineStr">
+        <is>
+          <t>乔木</t>
+        </is>
+      </c>
+      <c r="D263" s="8" t="inlineStr">
+        <is>
+          <t>居住区</t>
+        </is>
+      </c>
+      <c r="E263" s="8" t="n">
+        <v>2.0523</v>
+      </c>
+      <c r="F263" s="8" t="inlineStr"/>
+      <c r="G263" s="8" t="inlineStr"/>
+      <c r="H263" s="8" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="I263" s="8" t="n">
+        <v>221.63</v>
+      </c>
+      <c r="J263" s="8" t="n">
+        <v>125.53</v>
+      </c>
+      <c r="K263" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="L263" s="8" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="M263" s="8" t="inlineStr">
+        <is>
+          <t>冬季</t>
+        </is>
+      </c>
+      <c r="N263" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="O263" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P263" s="8" t="inlineStr">
+        <is>
+          <t>水洗法+滤膜称重</t>
+        </is>
+      </c>
+      <c r="Q263" s="8" t="inlineStr"/>
+      <c r="R263" s="8" t="inlineStr">
+        <is>
+          <t>韩世明, 2017, 东华理工大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S263" s="8" t="inlineStr"/>
+      <c r="T263" s="8" t="inlineStr">
+        <is>
+          <t>红岭花园三期;第1/2/3周=1.5432/2.1675/2.4463g/m²;6种中排名第3</t>
+        </is>
+      </c>
+      <c r="U263" s="8" t="inlineStr">
+        <is>
+          <t>居住区</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="8" t="inlineStr">
+        <is>
+          <t>柚子树</t>
+        </is>
+      </c>
+      <c r="B264" s="8" t="inlineStr">
+        <is>
+          <t>Citrus maxima</t>
+        </is>
+      </c>
+      <c r="C264" s="8" t="inlineStr">
+        <is>
+          <t>乔木</t>
+        </is>
+      </c>
+      <c r="D264" s="8" t="inlineStr">
+        <is>
+          <t>居住区</t>
+        </is>
+      </c>
+      <c r="E264" s="8" t="n">
+        <v>1.4588</v>
+      </c>
+      <c r="F264" s="8" t="inlineStr"/>
+      <c r="G264" s="8" t="inlineStr"/>
+      <c r="H264" s="8" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="I264" s="8" t="n">
+        <v>221.63</v>
+      </c>
+      <c r="J264" s="8" t="n">
+        <v>125.53</v>
+      </c>
+      <c r="K264" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="L264" s="8" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="M264" s="8" t="inlineStr">
+        <is>
+          <t>冬季</t>
+        </is>
+      </c>
+      <c r="N264" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="O264" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P264" s="8" t="inlineStr">
+        <is>
+          <t>水洗法+滤膜称重</t>
+        </is>
+      </c>
+      <c r="Q264" s="8" t="inlineStr"/>
+      <c r="R264" s="8" t="inlineStr">
+        <is>
+          <t>韩世明, 2017, 东华理工大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S264" s="8" t="inlineStr"/>
+      <c r="T264" s="8" t="inlineStr">
+        <is>
+          <t>红岭花园三期;第1/2/3周=1.2083/1.5546/1.6135g/m²;6种中排名第4</t>
+        </is>
+      </c>
+      <c r="U264" s="8" t="inlineStr">
+        <is>
+          <t>居住区</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="8" t="inlineStr">
+        <is>
+          <t>法国冬青</t>
+        </is>
+      </c>
+      <c r="B265" s="8" t="inlineStr">
+        <is>
+          <t>Viburnum odoratissimum</t>
+        </is>
+      </c>
+      <c r="C265" s="8" t="inlineStr">
+        <is>
+          <t>灌木</t>
+        </is>
+      </c>
+      <c r="D265" s="8" t="inlineStr">
+        <is>
+          <t>居住区</t>
+        </is>
+      </c>
+      <c r="E265" s="8" t="n">
+        <v>1.506</v>
+      </c>
+      <c r="F265" s="8" t="inlineStr"/>
+      <c r="G265" s="8" t="inlineStr"/>
+      <c r="H265" s="8" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="I265" s="8" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="J265" s="8" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="K265" s="8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="L265" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="M265" s="8" t="inlineStr">
+        <is>
+          <t>冬季</t>
+        </is>
+      </c>
+      <c r="N265" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="O265" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P265" s="8" t="inlineStr">
+        <is>
+          <t>水洗法+滤膜称重</t>
+        </is>
+      </c>
+      <c r="Q265" s="8" t="inlineStr"/>
+      <c r="R265" s="8" t="inlineStr">
+        <is>
+          <t>韩世明, 2017, 东华理工大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S265" s="8" t="inlineStr"/>
+      <c r="T265" s="8" t="inlineStr">
+        <is>
+          <t>奥克斯盛世经典;第1/2/3周=1.2158/1.5383/1.7638g/m²;8种中排名第1</t>
+        </is>
+      </c>
+      <c r="U265" s="8" t="inlineStr">
+        <is>
+          <t>居住区</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="8" t="inlineStr">
+        <is>
+          <t>杨梅</t>
+        </is>
+      </c>
+      <c r="B266" s="8" t="inlineStr">
+        <is>
+          <t>Myrica rubra</t>
+        </is>
+      </c>
+      <c r="C266" s="8" t="inlineStr">
+        <is>
+          <t>乔木</t>
+        </is>
+      </c>
+      <c r="D266" s="8" t="inlineStr">
+        <is>
+          <t>居住区</t>
+        </is>
+      </c>
+      <c r="E266" s="8" t="n">
+        <v>0.5793</v>
+      </c>
+      <c r="F266" s="8" t="inlineStr"/>
+      <c r="G266" s="8" t="inlineStr"/>
+      <c r="H266" s="8" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="I266" s="8" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="J266" s="8" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="K266" s="8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="L266" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="M266" s="8" t="inlineStr">
+        <is>
+          <t>冬季</t>
+        </is>
+      </c>
+      <c r="N266" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="O266" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P266" s="8" t="inlineStr">
+        <is>
+          <t>水洗法+滤膜称重</t>
+        </is>
+      </c>
+      <c r="Q266" s="8" t="inlineStr"/>
+      <c r="R266" s="8" t="inlineStr">
+        <is>
+          <t>韩世明, 2017, 东华理工大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S266" s="8" t="inlineStr"/>
+      <c r="T266" s="8" t="inlineStr">
+        <is>
+          <t>奥克斯盛世经典;第1/2/3周=0.4842/0.5410/0.7127g/m²;8种中排名第7</t>
+        </is>
+      </c>
+      <c r="U266" s="8" t="inlineStr">
+        <is>
+          <t>居住区</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="8" t="inlineStr">
+        <is>
+          <t>山茶</t>
+        </is>
+      </c>
+      <c r="B267" s="8" t="inlineStr">
+        <is>
+          <t>Camellia japonica</t>
+        </is>
+      </c>
+      <c r="C267" s="8" t="inlineStr">
+        <is>
+          <t>灌木</t>
+        </is>
+      </c>
+      <c r="D267" s="8" t="inlineStr">
+        <is>
+          <t>居住区</t>
+        </is>
+      </c>
+      <c r="E267" s="8" t="n">
+        <v>0.5481</v>
+      </c>
+      <c r="F267" s="8" t="inlineStr"/>
+      <c r="G267" s="8" t="inlineStr"/>
+      <c r="H267" s="8" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="I267" s="8" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="J267" s="8" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="K267" s="8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="L267" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="M267" s="8" t="inlineStr">
+        <is>
+          <t>冬季</t>
+        </is>
+      </c>
+      <c r="N267" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="O267" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P267" s="8" t="inlineStr">
+        <is>
+          <t>水洗法+滤膜称重</t>
+        </is>
+      </c>
+      <c r="Q267" s="8" t="inlineStr"/>
+      <c r="R267" s="8" t="inlineStr">
+        <is>
+          <t>韩世明, 2017, 东华理工大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S267" s="8" t="inlineStr"/>
+      <c r="T267" s="8" t="inlineStr">
+        <is>
+          <t>奥克斯盛世经典;第1/2/3周;8种中排名第8</t>
+        </is>
+      </c>
+      <c r="U267" s="8" t="inlineStr">
+        <is>
+          <t>居住区</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="8" t="inlineStr">
+        <is>
+          <t>紫薇</t>
+        </is>
+      </c>
+      <c r="B268" s="8" t="inlineStr">
+        <is>
+          <t>Lagerstroemia indica</t>
+        </is>
+      </c>
+      <c r="C268" s="8" t="inlineStr">
+        <is>
+          <t>灌木</t>
+        </is>
+      </c>
+      <c r="D268" s="8" t="inlineStr">
+        <is>
+          <t>城市混合</t>
+        </is>
+      </c>
+      <c r="E268" s="8" t="inlineStr"/>
+      <c r="F268" s="8" t="n">
+        <v>0.1536</v>
+      </c>
+      <c r="G268" s="8" t="n">
+        <v>0.0633</v>
+      </c>
+      <c r="H268" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I268" s="8" t="inlineStr"/>
+      <c r="J268" s="8" t="inlineStr"/>
+      <c r="K268" s="8" t="inlineStr"/>
+      <c r="L268" s="8" t="inlineStr"/>
+      <c r="M268" s="8" t="inlineStr">
+        <is>
+          <t>春季</t>
+        </is>
+      </c>
+      <c r="N268" s="8" t="inlineStr"/>
+      <c r="O268" s="8" t="inlineStr"/>
+      <c r="P268" s="8" t="inlineStr"/>
+      <c r="Q268" s="8" t="inlineStr"/>
+      <c r="R268" s="8" t="inlineStr">
+        <is>
+          <t>张冰洁, 2024, 华中农业大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S268" s="8" t="inlineStr"/>
+      <c r="T268" s="8" t="inlineStr">
+        <is>
+          <t>⚠柱状图人工读数;春季17种PM10+PM2.5双料最强(overall pooled)</t>
+        </is>
+      </c>
+      <c r="U268" s="8" t="inlineStr">
+        <is>
+          <t>城市混合</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="8" t="inlineStr">
+        <is>
+          <t>狗牙根</t>
+        </is>
+      </c>
+      <c r="B269" s="8" t="inlineStr">
+        <is>
+          <t>Cynodon dactylon</t>
+        </is>
+      </c>
+      <c r="C269" s="8" t="inlineStr">
+        <is>
+          <t>地被</t>
+        </is>
+      </c>
+      <c r="D269" s="8" t="inlineStr">
+        <is>
+          <t>城市混合</t>
+        </is>
+      </c>
+      <c r="E269" s="8" t="inlineStr"/>
+      <c r="F269" s="8" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="G269" s="8" t="inlineStr"/>
+      <c r="H269" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I269" s="8" t="inlineStr"/>
+      <c r="J269" s="8" t="inlineStr"/>
+      <c r="K269" s="8" t="inlineStr"/>
+      <c r="L269" s="8" t="inlineStr"/>
+      <c r="M269" s="8" t="inlineStr">
+        <is>
+          <t>夏季</t>
+        </is>
+      </c>
+      <c r="N269" s="8" t="inlineStr"/>
+      <c r="O269" s="8" t="inlineStr"/>
+      <c r="P269" s="8" t="inlineStr"/>
+      <c r="Q269" s="8" t="inlineStr"/>
+      <c r="R269" s="8" t="inlineStr">
+        <is>
+          <t>张冰洁, 2024, 华中农业大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S269" s="8" t="inlineStr"/>
+      <c r="T269" s="8" t="inlineStr">
+        <is>
+          <t>⚠柱状图人工读数;夏季17种PM10最强(overall pooled);暖季型草冬季休眠</t>
+        </is>
+      </c>
+      <c r="U269" s="8" t="inlineStr">
+        <is>
+          <t>城市混合</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="8" t="inlineStr">
+        <is>
+          <t>狗牙根</t>
+        </is>
+      </c>
+      <c r="B270" s="8" t="inlineStr">
+        <is>
+          <t>Cynodon dactylon</t>
+        </is>
+      </c>
+      <c r="C270" s="8" t="inlineStr">
+        <is>
+          <t>地被</t>
+        </is>
+      </c>
+      <c r="D270" s="8" t="inlineStr">
+        <is>
+          <t>公园清洁区</t>
+        </is>
+      </c>
+      <c r="E270" s="8" t="inlineStr"/>
+      <c r="F270" s="8" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="G270" s="8" t="n">
+        <v>0.0466</v>
+      </c>
+      <c r="H270" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I270" s="8" t="inlineStr"/>
+      <c r="J270" s="8" t="inlineStr"/>
+      <c r="K270" s="8" t="inlineStr"/>
+      <c r="L270" s="8" t="inlineStr"/>
+      <c r="M270" s="8" t="inlineStr">
+        <is>
+          <t>春季</t>
+        </is>
+      </c>
+      <c r="N270" s="8" t="inlineStr"/>
+      <c r="O270" s="8" t="inlineStr"/>
+      <c r="P270" s="8" t="inlineStr"/>
+      <c r="Q270" s="8" t="inlineStr"/>
+      <c r="R270" s="8" t="inlineStr">
+        <is>
+          <t>张冰洁, 2024, 华中农业大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S270" s="8" t="inlineStr"/>
+      <c r="T270" s="8" t="inlineStr">
+        <is>
+          <t>⚠柱状图人工读数;解放公园内部</t>
+        </is>
+      </c>
+      <c r="U270" s="8" t="inlineStr">
+        <is>
+          <t>公园清洁区</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="8" t="inlineStr">
+        <is>
+          <t>水杉</t>
+        </is>
+      </c>
+      <c r="B271" s="8" t="inlineStr">
+        <is>
+          <t>Metasequoia glyptostroboides</t>
+        </is>
+      </c>
+      <c r="C271" s="8" t="inlineStr">
+        <is>
+          <t>乔木</t>
+        </is>
+      </c>
+      <c r="D271" s="8" t="inlineStr">
+        <is>
+          <t>城市混合</t>
+        </is>
+      </c>
+      <c r="E271" s="8" t="inlineStr"/>
+      <c r="F271" s="8" t="inlineStr"/>
+      <c r="G271" s="8" t="n">
+        <v>0.0555</v>
+      </c>
+      <c r="H271" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I271" s="8" t="inlineStr"/>
+      <c r="J271" s="8" t="inlineStr"/>
+      <c r="K271" s="8" t="inlineStr"/>
+      <c r="L271" s="8" t="inlineStr"/>
+      <c r="M271" s="8" t="inlineStr">
+        <is>
+          <t>夏季</t>
+        </is>
+      </c>
+      <c r="N271" s="8" t="inlineStr"/>
+      <c r="O271" s="8" t="inlineStr"/>
+      <c r="P271" s="8" t="inlineStr"/>
+      <c r="Q271" s="8" t="inlineStr"/>
+      <c r="R271" s="8" t="inlineStr">
+        <is>
+          <t>张冰洁, 2024, 华中农业大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S271" s="8" t="inlineStr"/>
+      <c r="T271" s="8" t="inlineStr">
+        <is>
+          <t>⚠柱状图人工读数;夏季17种PM2.5最强(overall pooled);落叶乔木冬季未测</t>
+        </is>
+      </c>
+      <c r="U271" s="8" t="inlineStr">
+        <is>
+          <t>城市混合</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="8" t="inlineStr">
+        <is>
+          <t>水杉</t>
+        </is>
+      </c>
+      <c r="B272" s="8" t="inlineStr">
+        <is>
+          <t>Metasequoia glyptostroboides</t>
+        </is>
+      </c>
+      <c r="C272" s="8" t="inlineStr">
+        <is>
+          <t>乔木</t>
+        </is>
+      </c>
+      <c r="D272" s="8" t="inlineStr">
+        <is>
+          <t>公园清洁区</t>
+        </is>
+      </c>
+      <c r="E272" s="8" t="inlineStr"/>
+      <c r="F272" s="8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G272" s="8" t="inlineStr"/>
+      <c r="H272" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I272" s="8" t="inlineStr"/>
+      <c r="J272" s="8" t="inlineStr"/>
+      <c r="K272" s="8" t="inlineStr"/>
+      <c r="L272" s="8" t="inlineStr"/>
+      <c r="M272" s="8" t="inlineStr">
+        <is>
+          <t>春季</t>
+        </is>
+      </c>
+      <c r="N272" s="8" t="inlineStr"/>
+      <c r="O272" s="8" t="inlineStr"/>
+      <c r="P272" s="8" t="inlineStr"/>
+      <c r="Q272" s="8" t="inlineStr"/>
+      <c r="R272" s="8" t="inlineStr">
+        <is>
+          <t>张冰洁, 2024, 华中农业大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S272" s="8" t="inlineStr"/>
+      <c r="T272" s="8" t="inlineStr">
+        <is>
+          <t>⚠柱状图人工读数;解放公园内部;inside&gt;outside(异常)</t>
+        </is>
+      </c>
+      <c r="U272" s="8" t="inlineStr">
+        <is>
+          <t>公园清洁区</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="8" t="inlineStr">
+        <is>
+          <t>栾树</t>
+        </is>
+      </c>
+      <c r="B273" s="8" t="inlineStr">
+        <is>
+          <t>Koelreuteria paniculata</t>
+        </is>
+      </c>
+      <c r="C273" s="8" t="inlineStr">
+        <is>
+          <t>乔木</t>
+        </is>
+      </c>
+      <c r="D273" s="8" t="inlineStr">
+        <is>
+          <t>公园清洁区</t>
+        </is>
+      </c>
+      <c r="E273" s="8" t="inlineStr"/>
+      <c r="F273" s="8" t="inlineStr"/>
+      <c r="G273" s="8" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="H273" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I273" s="8" t="inlineStr"/>
+      <c r="J273" s="8" t="inlineStr"/>
+      <c r="K273" s="8" t="inlineStr"/>
+      <c r="L273" s="8" t="inlineStr"/>
+      <c r="M273" s="8" t="inlineStr">
+        <is>
+          <t>夏季</t>
+        </is>
+      </c>
+      <c r="N273" s="8" t="inlineStr"/>
+      <c r="O273" s="8" t="inlineStr"/>
+      <c r="P273" s="8" t="inlineStr"/>
+      <c r="Q273" s="8" t="inlineStr"/>
+      <c r="R273" s="8" t="inlineStr">
+        <is>
+          <t>张冰洁, 2024, 华中农业大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S273" s="8" t="inlineStr"/>
+      <c r="T273" s="8" t="inlineStr">
+        <is>
+          <t>⚠柱状图人工读数;解放公园内部;inside&gt;outside(异常)</t>
+        </is>
+      </c>
+      <c r="U273" s="8" t="inlineStr">
+        <is>
+          <t>公园清洁区</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="8" t="inlineStr">
+        <is>
+          <t>栾树</t>
+        </is>
+      </c>
+      <c r="B274" s="8" t="inlineStr">
+        <is>
+          <t>Koelreuteria paniculata</t>
+        </is>
+      </c>
+      <c r="C274" s="8" t="inlineStr">
+        <is>
+          <t>乔木</t>
+        </is>
+      </c>
+      <c r="D274" s="8" t="inlineStr">
+        <is>
+          <t>城市混合</t>
+        </is>
+      </c>
+      <c r="E274" s="8" t="inlineStr"/>
+      <c r="F274" s="8" t="inlineStr"/>
+      <c r="G274" s="8" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="H274" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I274" s="8" t="inlineStr"/>
+      <c r="J274" s="8" t="inlineStr"/>
+      <c r="K274" s="8" t="inlineStr"/>
+      <c r="L274" s="8" t="inlineStr"/>
+      <c r="M274" s="8" t="inlineStr">
+        <is>
+          <t>夏季</t>
+        </is>
+      </c>
+      <c r="N274" s="8" t="inlineStr"/>
+      <c r="O274" s="8" t="inlineStr"/>
+      <c r="P274" s="8" t="inlineStr"/>
+      <c r="Q274" s="8" t="inlineStr"/>
+      <c r="R274" s="8" t="inlineStr">
+        <is>
+          <t>张冰洁, 2024, 华中农业大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S274" s="8" t="inlineStr"/>
+      <c r="T274" s="8" t="inlineStr">
+        <is>
+          <t>⚠柱状图人工读数;解放公园外部</t>
+        </is>
+      </c>
+      <c r="U274" s="8" t="inlineStr">
+        <is>
+          <t>城市混合</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="8" t="inlineStr">
+        <is>
+          <t>枫杨</t>
+        </is>
+      </c>
+      <c r="B275" s="8" t="inlineStr">
+        <is>
+          <t>Pterocarya stenoptera</t>
+        </is>
+      </c>
+      <c r="C275" s="8" t="inlineStr">
+        <is>
+          <t>乔木</t>
+        </is>
+      </c>
+      <c r="D275" s="8" t="inlineStr">
+        <is>
+          <t>公园清洁区</t>
+        </is>
+      </c>
+      <c r="E275" s="8" t="inlineStr"/>
+      <c r="F275" s="8" t="inlineStr"/>
+      <c r="G275" s="8" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="H275" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I275" s="8" t="inlineStr"/>
+      <c r="J275" s="8" t="inlineStr"/>
+      <c r="K275" s="8" t="inlineStr"/>
+      <c r="L275" s="8" t="inlineStr"/>
+      <c r="M275" s="8" t="inlineStr">
+        <is>
+          <t>夏季</t>
+        </is>
+      </c>
+      <c r="N275" s="8" t="inlineStr"/>
+      <c r="O275" s="8" t="inlineStr"/>
+      <c r="P275" s="8" t="inlineStr"/>
+      <c r="Q275" s="8" t="inlineStr"/>
+      <c r="R275" s="8" t="inlineStr">
+        <is>
+          <t>张冰洁, 2024, 华中农业大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S275" s="8" t="inlineStr"/>
+      <c r="T275" s="8" t="inlineStr">
+        <is>
+          <t>⚠柱状图人工读数;解放公园内部;inside&gt;outside(异常)</t>
+        </is>
+      </c>
+      <c r="U275" s="8" t="inlineStr">
+        <is>
+          <t>公园清洁区</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="8" t="inlineStr">
+        <is>
+          <t>枫杨</t>
+        </is>
+      </c>
+      <c r="B276" s="8" t="inlineStr">
+        <is>
+          <t>Pterocarya stenoptera</t>
+        </is>
+      </c>
+      <c r="C276" s="8" t="inlineStr">
+        <is>
+          <t>乔木</t>
+        </is>
+      </c>
+      <c r="D276" s="8" t="inlineStr">
+        <is>
+          <t>城市混合</t>
+        </is>
+      </c>
+      <c r="E276" s="8" t="inlineStr"/>
+      <c r="F276" s="8" t="inlineStr"/>
+      <c r="G276" s="8" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="H276" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I276" s="8" t="inlineStr"/>
+      <c r="J276" s="8" t="inlineStr"/>
+      <c r="K276" s="8" t="inlineStr"/>
+      <c r="L276" s="8" t="inlineStr"/>
+      <c r="M276" s="8" t="inlineStr">
+        <is>
+          <t>夏季</t>
+        </is>
+      </c>
+      <c r="N276" s="8" t="inlineStr"/>
+      <c r="O276" s="8" t="inlineStr"/>
+      <c r="P276" s="8" t="inlineStr"/>
+      <c r="Q276" s="8" t="inlineStr"/>
+      <c r="R276" s="8" t="inlineStr">
+        <is>
+          <t>张冰洁, 2024, 华中农业大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S276" s="8" t="inlineStr"/>
+      <c r="T276" s="8" t="inlineStr">
+        <is>
+          <t>⚠柱状图人工读数;解放公园外部</t>
+        </is>
+      </c>
+      <c r="U276" s="8" t="inlineStr">
+        <is>
+          <t>城市混合</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="8" t="inlineStr">
+        <is>
+          <t>枫香</t>
+        </is>
+      </c>
+      <c r="B277" s="8" t="inlineStr">
+        <is>
+          <t>Liquidambar formosana</t>
+        </is>
+      </c>
+      <c r="C277" s="8" t="inlineStr">
+        <is>
+          <t>乔木</t>
+        </is>
+      </c>
+      <c r="D277" s="8" t="inlineStr">
+        <is>
+          <t>公园清洁区</t>
+        </is>
+      </c>
+      <c r="E277" s="8" t="inlineStr"/>
+      <c r="F277" s="8" t="n">
+        <v>0.0915</v>
+      </c>
+      <c r="G277" s="8" t="n">
+        <v>0.0334</v>
+      </c>
+      <c r="H277" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I277" s="8" t="inlineStr"/>
+      <c r="J277" s="8" t="inlineStr"/>
+      <c r="K277" s="8" t="inlineStr"/>
+      <c r="L277" s="8" t="inlineStr"/>
+      <c r="M277" s="8" t="inlineStr">
+        <is>
+          <t>春季</t>
+        </is>
+      </c>
+      <c r="N277" s="8" t="inlineStr"/>
+      <c r="O277" s="8" t="inlineStr"/>
+      <c r="P277" s="8" t="inlineStr"/>
+      <c r="Q277" s="8" t="inlineStr"/>
+      <c r="R277" s="8" t="inlineStr">
+        <is>
+          <t>张冰洁, 2024, 华中农业大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S277" s="8" t="inlineStr"/>
+      <c r="T277" s="8" t="inlineStr">
+        <is>
+          <t>⚠柱状图人工读数;解放公园内部;inside&gt;outside(异常)</t>
+        </is>
+      </c>
+      <c r="U277" s="8" t="inlineStr">
+        <is>
+          <t>公园清洁区</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="8" t="inlineStr">
+        <is>
+          <t>枫香</t>
+        </is>
+      </c>
+      <c r="B278" s="8" t="inlineStr">
+        <is>
+          <t>Liquidambar formosana</t>
+        </is>
+      </c>
+      <c r="C278" s="8" t="inlineStr">
+        <is>
+          <t>乔木</t>
+        </is>
+      </c>
+      <c r="D278" s="8" t="inlineStr">
+        <is>
+          <t>城市混合</t>
+        </is>
+      </c>
+      <c r="E278" s="8" t="inlineStr"/>
+      <c r="F278" s="8" t="n">
+        <v>0.0795</v>
+      </c>
+      <c r="G278" s="8" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="H278" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I278" s="8" t="inlineStr"/>
+      <c r="J278" s="8" t="inlineStr"/>
+      <c r="K278" s="8" t="inlineStr"/>
+      <c r="L278" s="8" t="inlineStr"/>
+      <c r="M278" s="8" t="inlineStr">
+        <is>
+          <t>春季</t>
+        </is>
+      </c>
+      <c r="N278" s="8" t="inlineStr"/>
+      <c r="O278" s="8" t="inlineStr"/>
+      <c r="P278" s="8" t="inlineStr"/>
+      <c r="Q278" s="8" t="inlineStr"/>
+      <c r="R278" s="8" t="inlineStr">
+        <is>
+          <t>张冰洁, 2024, 华中农业大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S278" s="8" t="inlineStr"/>
+      <c r="T278" s="8" t="inlineStr">
+        <is>
+          <t>⚠柱状图人工读数;解放公园外部</t>
+        </is>
+      </c>
+      <c r="U278" s="8" t="inlineStr">
+        <is>
+          <t>城市混合</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="8" t="inlineStr">
+        <is>
+          <t>鸡爪槭</t>
+        </is>
+      </c>
+      <c r="B279" s="8" t="inlineStr">
+        <is>
+          <t>Acer palmatum</t>
+        </is>
+      </c>
+      <c r="C279" s="8" t="inlineStr">
+        <is>
+          <t>灌木</t>
+        </is>
+      </c>
+      <c r="D279" s="8" t="inlineStr">
+        <is>
+          <t>公园清洁区</t>
+        </is>
+      </c>
+      <c r="E279" s="8" t="inlineStr"/>
+      <c r="F279" s="8" t="n">
+        <v>0.07580000000000001</v>
+      </c>
+      <c r="G279" s="8" t="inlineStr"/>
+      <c r="H279" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I279" s="8" t="inlineStr"/>
+      <c r="J279" s="8" t="inlineStr"/>
+      <c r="K279" s="8" t="inlineStr"/>
+      <c r="L279" s="8" t="inlineStr"/>
+      <c r="M279" s="8" t="inlineStr">
+        <is>
+          <t>夏季</t>
+        </is>
+      </c>
+      <c r="N279" s="8" t="inlineStr"/>
+      <c r="O279" s="8" t="inlineStr"/>
+      <c r="P279" s="8" t="inlineStr"/>
+      <c r="Q279" s="8" t="inlineStr"/>
+      <c r="R279" s="8" t="inlineStr">
+        <is>
+          <t>张冰洁, 2024, 华中农业大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S279" s="8" t="inlineStr"/>
+      <c r="T279" s="8" t="inlineStr">
+        <is>
+          <t>⚠柱状图人工读数;解放公园内部;inside&gt;outside(异常)</t>
+        </is>
+      </c>
+      <c r="U279" s="8" t="inlineStr">
+        <is>
+          <t>公园清洁区</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="8" t="inlineStr">
+        <is>
+          <t>鸡爪槭</t>
+        </is>
+      </c>
+      <c r="B280" s="8" t="inlineStr">
+        <is>
+          <t>Acer palmatum</t>
+        </is>
+      </c>
+      <c r="C280" s="8" t="inlineStr">
+        <is>
+          <t>灌木</t>
+        </is>
+      </c>
+      <c r="D280" s="8" t="inlineStr">
+        <is>
+          <t>城市混合</t>
+        </is>
+      </c>
+      <c r="E280" s="8" t="inlineStr"/>
+      <c r="F280" s="8" t="n">
+        <v>0.0707</v>
+      </c>
+      <c r="G280" s="8" t="inlineStr"/>
+      <c r="H280" s="8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="I280" s="8" t="inlineStr"/>
+      <c r="J280" s="8" t="inlineStr"/>
+      <c r="K280" s="8" t="inlineStr"/>
+      <c r="L280" s="8" t="inlineStr"/>
+      <c r="M280" s="8" t="inlineStr">
+        <is>
+          <t>夏季</t>
+        </is>
+      </c>
+      <c r="N280" s="8" t="inlineStr"/>
+      <c r="O280" s="8" t="inlineStr"/>
+      <c r="P280" s="8" t="inlineStr"/>
+      <c r="Q280" s="8" t="inlineStr"/>
+      <c r="R280" s="8" t="inlineStr">
+        <is>
+          <t>张冰洁, 2024, 华中农业大学硕士论文</t>
+        </is>
+      </c>
+      <c r="S280" s="8" t="inlineStr"/>
+      <c r="T280" s="8" t="inlineStr">
+        <is>
+          <t>⚠柱状图人工读数;解放公园外部</t>
+        </is>
+      </c>
+      <c r="U280" s="8" t="inlineStr">
+        <is>
+          <t>城市混合</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
